--- a/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/ticket_categories.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/09_servicenow_support_workload/ticket_categories.xlsx
@@ -472,11 +472,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>136</v>
+        <v>306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>79.4%</t>
         </is>
       </c>
     </row>
@@ -487,11 +487,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>632</v>
+        <v>312</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>73.0%</t>
         </is>
       </c>
     </row>
@@ -502,11 +502,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>606</v>
+        <v>689</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>91.0%</t>
         </is>
       </c>
     </row>
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108</v>
+        <v>158</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>70.7%</t>
         </is>
       </c>
     </row>
@@ -532,11 +532,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>883</v>
+        <v>270</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>74.5%</t>
         </is>
       </c>
     </row>
@@ -547,11 +547,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>613</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>64.6%</t>
         </is>
       </c>
     </row>
@@ -562,11 +562,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>493</v>
+        <v>575</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>74.4%</t>
         </is>
       </c>
     </row>
@@ -577,11 +577,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>685</v>
+        <v>577</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>97.4%</t>
         </is>
       </c>
     </row>
@@ -592,11 +592,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>343</v>
+        <v>486</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -607,11 +607,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>390</v>
+        <v>830</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
